--- a/data/trans_dic/P37A$medicoedad-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P37A$medicoedad-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,93%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,65; 6,63</t>
+          <t>2,53; 6,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,75; 8,83</t>
+          <t>3,77; 8,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,72; 11,71</t>
+          <t>6,06; 11,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11,32; 16,76</t>
+          <t>11,2; 16,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,19; 10,24</t>
+          <t>4,23; 9,78</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,68; 4,06</t>
+          <t>0,95; 4,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,47; 8,03</t>
+          <t>2,8; 8,26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,23; 11,41</t>
+          <t>7,69; 12,13</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,73; 6,97</t>
+          <t>3,81; 7,05</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,0; 6,06</t>
+          <t>3,03; 6,11</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,09; 9,11</t>
+          <t>5,16; 9,19</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10,09; 13,32</t>
+          <t>10,21; 13,72</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,59%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,96; 8,64</t>
+          <t>3,96; 8,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,39; 11,27</t>
+          <t>5,42; 11,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,45; 11,29</t>
+          <t>5,39; 10,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,64; 17,24</t>
+          <t>11,54; 17,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,87; 4,09</t>
+          <t>0,86; 3,96</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,48; 5,79</t>
+          <t>1,45; 5,6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,0; 6,16</t>
+          <t>1,91; 5,66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,56; 10,82</t>
+          <t>6,6; 10,91</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,76; 5,74</t>
+          <t>2,79; 5,58</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,09; 8,06</t>
+          <t>4,1; 7,82</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,18; 7,58</t>
+          <t>4,1; 7,58</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,67; 13,39</t>
+          <t>9,9; 13,45</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>17,15%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,01; 7,81</t>
+          <t>4,08; 7,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,33; 11,2</t>
+          <t>6,26; 11,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,26; 12,86</t>
+          <t>8,0; 13,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,56; 15,84</t>
+          <t>12,08; 17,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,96; 10,18</t>
+          <t>2,56; 10,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,49; 10,64</t>
+          <t>4,09; 10,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,42; 17,7</t>
+          <t>6,66; 18,46</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,76; 29,05</t>
+          <t>18,65; 28,03</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,07; 7,57</t>
+          <t>4,14; 7,66</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,33; 10,37</t>
+          <t>6,23; 9,96</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,19; 13,12</t>
+          <t>8,24; 13,14</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,33; 18,18</t>
+          <t>14,94; 19,78</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>13,0%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,98; 10,03</t>
+          <t>6,9; 10,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,36; 13,4</t>
+          <t>9,52; 13,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,85; 11,28</t>
+          <t>7,76; 11,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,13; 17,12</t>
+          <t>13,02; 16,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,83; 7,31</t>
+          <t>3,97; 7,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,95; 5,98</t>
+          <t>2,91; 5,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,79; 8,51</t>
+          <t>4,73; 8,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,24; 57,13</t>
+          <t>9,07; 12,21</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,15; 8,3</t>
+          <t>6,26; 8,6</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,29; 9,92</t>
+          <t>7,22; 9,83</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,93; 9,41</t>
+          <t>6,95; 9,32</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,91; 47,94</t>
+          <t>11,79; 14,26</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>16,03%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,96; 12,01</t>
+          <t>5,67; 11,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,57; 16,61</t>
+          <t>10,64; 16,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,47; 15,39</t>
+          <t>10,4; 15,55</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,81; 16,72</t>
+          <t>9,78; 14,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,17; 10,98</t>
+          <t>6,09; 10,8</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,53; 14,03</t>
+          <t>9,4; 14,08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,15; 12,83</t>
+          <t>8,23; 12,55</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12,93; 20,09</t>
+          <t>16,85; 20,85</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,68; 10,25</t>
+          <t>6,59; 10,35</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10,54; 14,16</t>
+          <t>10,55; 14,34</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9,87; 13,28</t>
+          <t>9,7; 13,07</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,03; 17,74</t>
+          <t>14,58; 17,81</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,47%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,88</t>
+          <t>0,0; 1,34</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,73; 4,02</t>
+          <t>0,73; 4,11</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,3</t>
+          <t>0,36; 3,66</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,62; 3,59</t>
+          <t>0,52; 3,71</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>14,43; 18,66</t>
+          <t>14,34; 18,64</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16,72; 21,54</t>
+          <t>16,61; 21,53</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16,1; 21,42</t>
+          <t>15,91; 21,01</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>23,88; 29,1</t>
+          <t>23,56; 28,31</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11,65; 15,26</t>
+          <t>11,7; 15,25</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13,74; 17,78</t>
+          <t>13,68; 17,8</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>13,06; 17,03</t>
+          <t>12,76; 17,13</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>18,32; 22,7</t>
+          <t>18,31; 22,75</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>14,79%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,58; 7,16</t>
+          <t>5,56; 7,14</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,24; 10,26</t>
+          <t>8,25; 10,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,26; 10,05</t>
+          <t>8,16; 10,26</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10,1; 13,81</t>
+          <t>12,2; 14,26</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,8; 10,78</t>
+          <t>8,62; 10,72</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,26; 11,39</t>
+          <t>9,15; 11,33</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,6; 11,84</t>
+          <t>9,61; 11,9</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>15,64; 35,55</t>
+          <t>15,24; 17,19</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,45; 8,8</t>
+          <t>7,43; 8,78</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9,06; 10,51</t>
+          <t>9,07; 10,57</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9,24; 10,68</t>
+          <t>9,23; 10,72</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>13,75; 25,63</t>
+          <t>14,06; 15,49</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>69542</t>
+          <t>76546</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>41000</t>
+          <t>47358</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>110542</t>
+          <t>123904</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>12542; 31423</t>
+          <t>12000; 32687</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>16388; 38623</t>
+          <t>16493; 38471</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>24560; 50230</t>
+          <t>26010; 51130</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>57201; 84657</t>
+          <t>61682; 91552</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>12835; 31403</t>
+          <t>12961; 29979</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2148; 12767</t>
+          <t>2987; 12618</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8557; 27874</t>
+          <t>9702; 28662</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>32362; 51065</t>
+          <t>37553; 59234</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>29148; 54411</t>
+          <t>29749; 55033</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22580; 45516</t>
+          <t>22788; 45942</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>39488; 70694</t>
+          <t>40026; 71350</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>96115; 126935</t>
+          <t>106121; 142520</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>63511</t>
+          <t>68896</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>32405</t>
+          <t>36145</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>95916</t>
+          <t>105041</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14517; 31720</t>
+          <t>14517; 32033</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22583; 47195</t>
+          <t>22681; 48447</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20575; 42574</t>
+          <t>20327; 40909</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>52637; 77954</t>
+          <t>55782; 83373</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3246; 15212</t>
+          <t>3201; 14714</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5013; 19577</t>
+          <t>4893; 18931</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7433; 22939</t>
+          <t>7120; 21084</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>25084; 41393</t>
+          <t>27943; 46152</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>20401; 42388</t>
+          <t>20633; 41246</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>30980; 60964</t>
+          <t>31051; 59192</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>31315; 56779</t>
+          <t>30740; 56782</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>80740; 111761</t>
+          <t>89771; 121866</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>63317</t>
+          <t>69379</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>39541</t>
+          <t>43681</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>102858</t>
+          <t>113060</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>21745; 42351</t>
+          <t>22116; 42590</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>39853; 70501</t>
+          <t>39414; 71019</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>37880; 67130</t>
+          <t>41731; 68308</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23788; 105838</t>
+          <t>56964; 83657</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4966; 17082</t>
+          <t>4295; 17122</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11683; 27679</t>
+          <t>10628; 27954</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10671; 29401</t>
+          <t>11066; 30669</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>31307; 48483</t>
+          <t>34962; 52562</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>28906; 53764</t>
+          <t>29412; 54369</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>56324; 92223</t>
+          <t>55397; 88589</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>56343; 90267</t>
+          <t>56690; 90375</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>44502; 151824</t>
+          <t>98491; 130380</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>155635</t>
+          <t>167632</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>288287</t>
+          <t>91496</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>443922</t>
+          <t>259128</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>86405; 124215</t>
+          <t>85499; 124083</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>108538; 155282</t>
+          <t>110288; 153831</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>90214; 129696</t>
+          <t>89209; 126914</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>135887; 177150</t>
+          <t>147341; 190280</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>27383; 52248</t>
+          <t>28378; 53474</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22654; 45867</t>
+          <t>22344; 45932</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>39547; 70252</t>
+          <t>39088; 71300</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>100129; 558810</t>
+          <t>78128; 105119</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>120036; 162081</t>
+          <t>122170; 167934</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>140329; 191024</t>
+          <t>138973; 189208</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>136883; 185921</t>
+          <t>137339; 184118</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>259794; 964957</t>
+          <t>234972; 284273</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>63929</t>
+          <t>68490</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>145591</t>
+          <t>155708</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>209520</t>
+          <t>224198</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>20889; 42119</t>
+          <t>19872; 41213</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>53995; 84832</t>
+          <t>54302; 84744</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>64974; 95506</t>
+          <t>64546; 96496</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>51358; 79443</t>
+          <t>55559; 81274</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>35064; 62467</t>
+          <t>34635; 61417</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>72577; 106858</t>
+          <t>71554; 107200</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>60146; 94744</t>
+          <t>60735; 92624</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>108767; 169042</t>
+          <t>139984; 173256</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>61401; 94272</t>
+          <t>60588; 95104</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>134071; 180194</t>
+          <t>134190; 182418</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>134134; 180518</t>
+          <t>131847; 177619</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>171508; 233525</t>
+          <t>204009; 249089</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3739</t>
+          <t>3886</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>201545</t>
+          <t>217490</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>205284</t>
+          <t>221376</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 5621</t>
+          <t>0; 3998</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1942; 10736</t>
+          <t>1938; 10975</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1019; 9471</t>
+          <t>1021; 10517</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1484; 8639</t>
+          <t>1226; 8807</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>180226; 233001</t>
+          <t>179041; 232766</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>185473; 238904</t>
+          <t>184314; 238876</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>174205; 231729</t>
+          <t>172112; 227291</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>181778; 221527</t>
+          <t>198876; 239008</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>180247; 236112</t>
+          <t>181016; 235904</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>189156; 244742</t>
+          <t>188312; 244933</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>178881; 233125</t>
+          <t>174639; 234583</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>183569; 227384</t>
+          <t>198002; 246059</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>419673</t>
+          <t>454828</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>748369</t>
+          <t>591878</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1168042</t>
+          <t>1046706</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>182316; 234155</t>
+          <t>181735; 233513</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282014; 350949</t>
+          <t>282414; 350551</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>279619; 340363</t>
+          <t>276262; 347332</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>341009; 466342</t>
+          <t>419838; 491043</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>297233; 364299</t>
+          <t>291208; 362169</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>328841; 404413</t>
+          <t>324927; 402298</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>339148; 418193</t>
+          <t>339432; 420181</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>559647; 1271756</t>
+          <t>554079; 624753</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>495334; 585317</t>
+          <t>493747; 583543</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>632010; 732482</t>
+          <t>632678; 736674</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>639285; 738555</t>
+          <t>638702; 741585</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>955903; 1782519</t>
+          <t>995127; 1096659</t>
         </is>
       </c>
     </row>
